--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cfbf2d641072903/Desktop/スイミングダッシュボード/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{702DD6D6-6098-4158-8672-3F8A9DDCD954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A51B517-9C38-4926-A6A1-6B7B1ED66938}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{0DD07BAA-57FB-4478-9AF7-3BD925F329F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D44B094-FD01-489A-9BDF-EBC9AAB5DA50}"/>
   <bookViews>
-    <workbookView xWindow="5808" yWindow="996" windowWidth="13716" windowHeight="9960" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="バッタ" sheetId="1" r:id="rId1"/>
@@ -40,14 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="21">
-  <si>
-    <t>日付</t>
-    <rPh sb="0" eb="2">
-      <t>ヒヅケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="21">
   <si>
     <t>長水路 or 短水路</t>
     <rPh sb="0" eb="3">
@@ -101,20 +94,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>距離 (m)</t>
-    <rPh sb="0" eb="2">
-      <t>キョリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>タイム (秒)</t>
-    <rPh sb="5" eb="6">
-      <t>ビョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>50m 更新日</t>
     <rPh sb="4" eb="7">
       <t>コウシンビ</t>
@@ -153,10 +132,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2025/11/31</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>小5</t>
     <rPh sb="0" eb="1">
       <t>ショウ</t>
@@ -164,10 +139,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2026/4/218</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>日付</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -180,6 +151,26 @@
   </si>
   <si>
     <t>タイム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4'52"00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4'17"24</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3'50"98</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3'44"22</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3'35"70</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -190,9 +181,9 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="178" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="179" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,33 +205,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -270,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -287,22 +258,16 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -320,10 +285,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -602,54 +563,54 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="2">
+      <c r="A2" s="9">
         <v>45823</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1">
         <v>58.49</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
         <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
@@ -668,137 +629,137 @@
         <v>45984</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="2">
+      <c r="A3" s="9">
         <v>45956</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1">
         <v>52.07</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="4"/>
       <c r="M3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="2">
+      <c r="A4" s="9">
         <v>45984</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
         <v>51.12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="2">
+      <c r="A5" s="9">
         <v>46033</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1">
         <v>53</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="2">
+      <c r="A6" s="9">
         <v>46055</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1">
         <v>49.85</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="2">
+      <c r="A7" s="9">
         <v>46075</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1">
         <v>53.89</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
+      <c r="A8" s="9">
+        <v>46130</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1">
         <v>52.64</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -838,34 +799,34 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -873,19 +834,19 @@
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3">
         <v>58.72</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
         <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
@@ -904,7 +865,7 @@
         <v>46075</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -912,23 +873,23 @@
         <v>45815</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3">
         <v>56.3</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="4"/>
       <c r="O3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -936,19 +897,19 @@
         <v>45823</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3">
         <v>55.74</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -956,22 +917,22 @@
         <v>45844</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="3">
         <v>56.07</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -979,22 +940,22 @@
         <v>45942</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3">
         <v>52.11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1002,19 +963,19 @@
         <v>45956</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3">
         <v>49.12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1022,19 +983,19 @@
         <v>45984</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="3">
         <v>50.03</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1042,19 +1003,19 @@
         <v>46055</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3">
         <v>48.34</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1062,19 +1023,19 @@
         <v>46075</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1">
         <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="3">
         <v>48.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1082,19 +1043,19 @@
         <v>46130</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3">
         <v>48.72</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1129,34 +1090,34 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -1164,19 +1125,19 @@
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1">
         <v>68.260000000000005</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
         <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
@@ -1195,7 +1156,7 @@
         <v>46130</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1203,23 +1164,23 @@
         <v>45815</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
         <v>66.84</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="4"/>
       <c r="O3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1227,19 +1188,19 @@
         <v>45844</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
         <v>60.52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1247,22 +1208,22 @@
         <v>45955</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1">
         <v>56.15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1270,22 +1231,22 @@
         <v>46033</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1">
         <v>57.26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1293,19 +1254,19 @@
         <v>46075</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1">
         <v>56.39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1313,19 +1274,19 @@
         <v>46130</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="1">
         <v>54.31</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1363,34 +1324,34 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -1398,19 +1359,19 @@
         <v>45788</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1">
         <v>50.61</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
         <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
@@ -1429,7 +1390,7 @@
         <v>46075</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1437,23 +1398,23 @@
         <v>45816</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
         <v>49.82</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" s="4"/>
       <c r="O3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1461,19 +1422,19 @@
         <v>45823</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1">
         <v>48.98</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1481,22 +1442,22 @@
         <v>45844</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1">
         <v>46.9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1504,22 +1465,22 @@
         <v>45942</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1">
         <v>44.07</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1527,19 +1488,19 @@
         <v>45955</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1">
         <v>43.01</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1547,19 +1508,19 @@
         <v>45984</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
         <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="1">
         <v>42.75</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1567,19 +1528,19 @@
         <v>46033</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1">
         <v>42.36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1587,19 +1548,19 @@
         <v>46055</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1">
         <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1">
         <v>41.5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1607,19 +1568,19 @@
         <v>46075</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
         <v>42.24</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1627,19 +1588,19 @@
         <v>46130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="1">
         <v>40.99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1661,210 +1622,157 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F93145A-20C7-4E83-AE6C-04CD541B3421}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.796875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="14.8984375" style="1"/>
     <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.8984375" style="1"/>
-    <col min="7" max="7" width="21.8984375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.8984375" style="5"/>
-    <col min="9" max="9" width="20.296875" style="1" customWidth="1"/>
-    <col min="10" max="13" width="14.8984375" style="1"/>
-    <col min="14" max="14" width="9.8984375" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="14.8984375" style="1"/>
+    <col min="6" max="9" width="14.8984375" style="1"/>
+    <col min="10" max="10" width="9.8984375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="14.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="22.8" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:9" ht="17.399999999999999" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="6">
+        <v>45710</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7">
+        <v>200</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="8">
-        <v>45710</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="9">
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="6">
+        <v>45808</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7">
         <v>200</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="9">
-        <v>292</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="9">
-        <f>_xlfn.MINIFS(E:E, C:C, 200, D:D, "短水路")</f>
-        <v>215.7</v>
-      </c>
-      <c r="H2" s="11">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "短水路"), E:E, 0))</f>
+      <c r="D3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="6">
+        <v>45899</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7">
+        <v>200</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="6">
+        <v>45991</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7">
+        <v>200</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="6">
         <v>46081</v>
       </c>
-      <c r="I2" s="10">
-        <f>_xlfn.MINIFS(E:E, C:C, 200, D:D, "長水路")</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="11" t="e">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="8">
-        <v>45808</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="9">
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7">
         <v>200</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="9">
-        <v>242.24</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="9">
-        <f>INT(G2/60)</f>
-        <v>3</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="M3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="8">
-        <v>45899</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="9">
-        <v>200</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="9">
-        <v>230.98</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="9">
-        <f>MOD(G2,60)</f>
-        <v>35.699999999999989</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="9">
-        <v>200</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="9">
-        <v>224.22</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="4">
-        <f>TIME(0, G3, G4)</f>
-        <v>2.488425925925926E-3</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="8">
-        <v>46081</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="9">
-        <v>200</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="9">
-        <v>215.7</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="G8" s="4"/>
+      <c r="D6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D181" xr:uid="{FCD6C6B0-9EE2-40C6-BADA-61DB1F834B29}">
-      <formula1>$M$2:$M$3</formula1>
+      <formula1>$I$2:$I$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F20" xr:uid="{4F3B2A47-C23A-4C80-87FE-9C03E8B410ED}">
-      <formula1>$M$5:$M$6</formula1>
+      <formula1>$I$5:$I$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1686,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2007,32 +2007,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46137</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>36.21</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1686,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2007,6 +2007,32 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -2021,11 +2021,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>33.01</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>0.03</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1686,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2007,32 +2007,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46144</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1686,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2007,6 +2007,32 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -2021,11 +2021,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>33.33</v>
+        <v>34.33</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1686,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2007,32 +2007,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46145</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>34.33</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1686,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2007,6 +2007,32 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="バック" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ブレ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -468,313 +468,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.796875" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
-    <col width="14.8984375" customWidth="1" style="1" min="2" max="8"/>
-    <col width="25.5" customWidth="1" style="1" min="9" max="9"/>
-    <col width="14.8984375" customWidth="1" style="1" min="10" max="14"/>
-    <col width="9.8984375" customWidth="1" style="1" min="15" max="15"/>
-    <col width="14.8984375" customWidth="1" style="1" min="16" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>学年</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>距離</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>長水路 or 短水路</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>タイム</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>会場</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(短水路)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(長水路)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="n">
-        <v>45823</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>58.49</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
-        <v/>
-      </c>
-      <c r="H2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "短水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="I2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "長水路")</f>
-        <v/>
-      </c>
-      <c r="J2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="n">
-        <v>45956</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>52.64</v>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="D9:D178" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation sqref="F9:F132 K2:K132" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$N$3:$N$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$M$2:$M$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$M$5:$M$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
@@ -1153,7 +846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1457,7 +1150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1680,7 +1373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2036,4 +1729,258 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>学年</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>距離</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>長水路or短水路</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>タイム</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>会場</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="バック" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ブレ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ブレ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バッタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -468,390 +468,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.796875" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
-    <col width="14.8984375" customWidth="1" style="1" min="2" max="4"/>
-    <col width="14.8984375" customWidth="1" style="12" min="5" max="5"/>
-    <col width="14.8984375" customWidth="1" style="1" min="6" max="8"/>
-    <col width="22" customWidth="1" style="1" min="9" max="9"/>
-    <col width="14.8984375" customWidth="1" style="1" min="10" max="15"/>
-    <col width="9.8984375" customWidth="1" style="1" min="16" max="16"/>
-    <col width="14.8984375" customWidth="1" style="1" min="17" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>学年</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>距離</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>長水路 or 短水路</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>タイム</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>会場</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(短水路)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(長水路)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="n">
-        <v>45788</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="n">
-        <v>58.72</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
-        <v/>
-      </c>
-      <c r="H2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "短水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="I2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "長水路")</f>
-        <v/>
-      </c>
-      <c r="J2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="n">
-        <v>45815</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="n">
-        <v>45823</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>55.74</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="n">
-        <v>45844</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>56.07</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="n">
-        <v>45942</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>52.11</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="n">
-        <v>45956</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>50.03</v>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="D2:D181" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$O$2:$O$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F181 M2:M181" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$O$5:$O$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K132" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$N$3:$N$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
   <cols>
@@ -1150,7 +766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1373,7 +989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1723,6 +1339,260 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>学年</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>距離</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>長水路or短水路</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>タイム</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>会場</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1774,7 +1644,7 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1790,7 +1660,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.49</v>
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1800,7 +1670,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45956</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1812,11 +1682,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52.07</v>
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1826,7 +1696,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45984</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1838,11 +1708,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>51.12</v>
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1852,7 +1722,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>46033</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1864,11 +1734,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1878,7 +1748,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46055</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1890,11 +1760,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.85</v>
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1904,7 +1774,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1916,11 +1786,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53.89</v>
+        <v>49.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1930,11 +1800,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>46130</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1942,39 +1812,117 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>52.64</v>
+        <v>50.03</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
         <v>46152</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1924,7 +1924,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="ブレ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="バッタ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="バッタ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バック" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -772,220 +772,355 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.796875" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
-    <col width="14.8984375" customWidth="1" style="1" min="2" max="4"/>
-    <col width="17" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
-    <col width="14.8984375" customWidth="1" style="1" min="6" max="9"/>
-    <col width="9.8984375" customWidth="1" style="1" min="10" max="10"/>
-    <col width="14.8984375" customWidth="1" style="1" min="11" max="16384"/>
-  </cols>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>学年</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>長水路 or 短水路</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>長水路or短水路</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>タイム</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>会場</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="n">
-        <v>45710</v>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>小3</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>4'52"00</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="A2" s="14" t="n">
+        <v>45788</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>45816</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>45844</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>45942</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>45955</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="n">
-        <v>45808</v>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>4'17"24</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="n">
-        <v>45899</v>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>3'50"98</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>45991</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>3'44"22</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>46081</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>3'35"70</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="D2:D181" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$I$2:$I$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$I$5:$I$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -995,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,7 +1167,7 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1048,7 +1183,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>58.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1058,7 +1193,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1070,11 +1205,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>52.07</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1084,7 +1219,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45984</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1096,11 +1231,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>51.12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1110,7 +1245,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>46033</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1122,11 +1257,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1136,7 +1271,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46055</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1148,11 +1283,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>49.85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1297,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1174,11 +1309,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>53.89</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1188,11 +1323,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1200,25 +1335,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>52.64</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46152</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1230,115 +1365,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>49.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1390,7 +1421,7 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1406,7 +1437,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.49</v>
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1416,7 +1447,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45956</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1428,11 +1459,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52.07</v>
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1442,7 +1473,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45984</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1454,11 +1485,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>51.12</v>
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1468,7 +1499,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>46033</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1480,11 +1511,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1494,7 +1525,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46055</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1506,11 +1537,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.85</v>
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1520,7 +1551,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1532,11 +1563,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53.89</v>
+        <v>49.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1546,11 +1577,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>46130</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1558,41 +1589,119 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>52.64</v>
+        <v>50.03</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
         <v>46152</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1644,33 +1753,35 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.72</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'52"00</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1678,25 +1789,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>56.3</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'17"24</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1704,25 +1817,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>55.74</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'50"98</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1730,25 +1845,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>56.07</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'44"22</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1756,33 +1873,35 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>52.11</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'35"70</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>46172</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1790,141 +1909,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>207.18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>50.03</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>45.85</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="ブレ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="フリー" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="バッタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="バック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="メドレー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1384,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,33 +1421,35 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45788</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.72</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'52"00</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1455,25 +1457,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>56.3</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'17"24</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1481,25 +1485,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>55.74</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'50"98</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1507,25 +1513,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>56.07</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'44"22</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1533,33 +1541,35 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>52.11</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'35"70</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>46172</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1567,141 +1577,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>207.18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>50.03</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>45.85</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1753,35 +1633,33 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小3</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'52"00</t>
-        </is>
+      <c r="E2" t="n">
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1789,27 +1667,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'17"24</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1817,27 +1693,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'50"98</t>
-        </is>
+      <c r="E4" t="n">
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1845,27 +1719,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'44"22</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1873,47 +1745,201 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'35"70</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46172</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>207.18</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="ブレ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="フリー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="バッタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="メドレー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="バッタ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バック" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,7 +809,7 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>58.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -847,11 +847,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>52.07</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45984</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -873,11 +873,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>51.12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>46033</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46055</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -925,11 +925,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>49.85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -951,11 +951,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>53.89</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -965,11 +965,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -977,25 +977,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>52.64</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46152</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1007,115 +1007,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>49.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,33 +1063,35 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45823</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.49</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'52"00</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45956</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1201,25 +1099,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>52.07</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'17"24</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45984</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1227,25 +1127,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>51.12</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'50"98</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>46033</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1253,25 +1155,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>53</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'44"22</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46055</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1279,95 +1183,45 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>49.85</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'35"70</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>46172</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53.89</v>
+        <v>207.18</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>52.64</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -1384,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,35 +1275,33 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小3</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'52"00</t>
-        </is>
+      <c r="E2" t="n">
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1457,27 +1309,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'17"24</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1485,27 +1335,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'50"98</t>
-        </is>
+      <c r="E4" t="n">
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1513,27 +1361,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'44"22</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1541,47 +1387,201 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'35"70</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46172</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>207.18</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.72</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56.3</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55.74</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.07</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52.11</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50.03</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46055</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48.34</v>
+        <v>42.36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46075</v>
+        <v>46055</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1853,11 +1853,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1867,11 +1867,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1879,21 +1879,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48.72</v>
+        <v>42.24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1909,17 +1909,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45.85</v>
+        <v>40.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>46179</v>
+        <v>46152</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1931,13 +1931,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ブレ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="バッタ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="メドレー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="バック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="バック" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -468,301 +468,251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.8984375" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="15.796875" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
-    <col width="14.8984375" customWidth="1" style="1" min="2" max="8"/>
-    <col width="22.09765625" customWidth="1" style="1" min="9" max="9"/>
-    <col width="14.8984375" customWidth="1" style="1" min="10" max="15"/>
-    <col width="9.8984375" customWidth="1" style="1" min="16" max="16"/>
-    <col width="14.8984375" customWidth="1" style="1" min="17" max="16384"/>
-  </cols>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>学年</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>長水路 or 短水路</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>長水路or短水路</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>タイム</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>会場</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(短水路)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>50m ベストタイム(長水路)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>50m 更新日</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
-        <v>45788</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>68.26000000000001</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "短水路")</f>
-        <v/>
-      </c>
-      <c r="H2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "短水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="I2" s="1">
-        <f>_xlfn.MINIFS(E:E, C:C, 50, D:D, "長水路")</f>
-        <v/>
-      </c>
-      <c r="J2" s="5">
-        <f>INDEX(A:A, MATCH(_xlfn.MINIFS(E:E, D:D, "長水路"), E:E, 0))</f>
-        <v/>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="A2" s="14" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>45956</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="n">
-        <v>45815</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E4" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>66.84</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="n">
-        <v>45844</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="n">
-        <v>45955</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>56.15</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="E7" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="n">
-        <v>46033</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>57.26</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>56.39</v>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>54.31</v>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="F2:F8 M2:M5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$O$5:$O$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D180" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$O$2:$O$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K132" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>$N$3:$N$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -772,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,33 +759,35 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45823</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.49</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'52"00</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45956</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -843,25 +795,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>52.07</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'17"24</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45984</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -869,25 +823,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>51.12</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'50"98</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>46033</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -895,25 +851,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>53</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'44"22</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46055</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -921,95 +879,45 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>49.85</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'35"70</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>46172</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53.89</v>
+        <v>207.18</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>52.64</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -1026,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,35 +971,33 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小3</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'52"00</t>
-        </is>
+      <c r="E2" t="n">
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1099,27 +1005,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'17"24</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1127,27 +1031,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'50"98</t>
-        </is>
+      <c r="E4" t="n">
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1155,27 +1057,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'44"22</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1183,47 +1083,201 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'35"70</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46172</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>207.18</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,7 +1345,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.72</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1301,7 +1355,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1317,7 +1371,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56.3</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1343,7 +1397,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55.74</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1369,7 +1423,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.07</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1395,7 +1449,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52.11</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1405,7 +1459,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1421,7 +1475,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1447,7 +1501,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50.03</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1511,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46055</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1473,7 +1527,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48.34</v>
+        <v>42.36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1483,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46075</v>
+        <v>46055</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1495,11 +1549,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1509,11 +1563,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1521,21 +1575,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48.72</v>
+        <v>42.24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1551,17 +1605,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45.85</v>
+        <v>40.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>46179</v>
+        <v>46152</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1573,13 +1627,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1596,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1649,7 +1729,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1659,7 +1739,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1675,7 +1755,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>66.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1685,7 +1765,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1697,11 +1777,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>60.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1711,7 +1791,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45955</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1723,11 +1803,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>56.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1737,7 +1817,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46033</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1749,11 +1829,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>57.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1763,7 +1843,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1775,11 +1855,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>56.39</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1789,11 +1869,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1805,21 +1885,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>54.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46180</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1827,143 +1907,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>53.01</v>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="F14" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="バック" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1292,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>66.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1393,11 +1393,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>60.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45955</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1419,11 +1419,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>56.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46033</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1445,11 +1445,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>57.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1471,11 +1471,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>56.39</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1485,11 +1485,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>54.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46180</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1523,143 +1523,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>53.01</v>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>46055</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="F14" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1676,7 +1546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,7 +1599,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.26000000000001</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1739,7 +1609,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1755,7 +1625,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.84</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1765,7 +1635,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1777,11 +1647,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60.52</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1791,7 +1661,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45955</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1803,11 +1673,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.15</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1817,7 +1687,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46033</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1829,11 +1699,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.26</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1843,7 +1713,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1855,11 +1725,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56.39</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1869,11 +1739,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>46130</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1885,35 +1755,191 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.31</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
         <v>46180</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>53.01</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -9,8 +9,8 @@
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="バック" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1292,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.26000000000001</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.84</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1393,11 +1393,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60.52</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45955</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1419,11 +1419,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.15</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46033</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1445,11 +1445,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.26</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1471,11 +1471,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56.39</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1485,11 +1485,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>46130</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1501,35 +1501,191 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.31</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
         <v>46180</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>53.01</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1546,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1599,7 +1755,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1609,7 +1765,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1625,7 +1781,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>66.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1635,7 +1791,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1647,11 +1803,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>60.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1661,7 +1817,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45955</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1673,11 +1829,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>56.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1687,7 +1843,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46033</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1699,11 +1855,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>57.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1713,7 +1869,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1725,11 +1881,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>56.39</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1739,11 +1895,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1755,21 +1911,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>54.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46180</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1777,11 +1933,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>53.01</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1791,11 +1947,11 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46055</v>
+        <v>46187</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1807,139 +1963,9 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>41.5</v>
+        <v>52.53</v>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="バック" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -934,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.72</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56.3</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55.74</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.07</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52.11</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50.03</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46055</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48.34</v>
+        <v>42.36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46075</v>
+        <v>46055</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1191,11 +1191,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1205,11 +1205,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1217,21 +1217,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48.72</v>
+        <v>42.24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1247,17 +1247,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45.85</v>
+        <v>40.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>46179</v>
+        <v>46152</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1269,13 +1269,65 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>長水路</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>47.75</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1292,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,7 +1397,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1355,7 +1407,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1371,7 +1423,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>66.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1381,7 +1433,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1393,11 +1445,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>60.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1407,7 +1459,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45955</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1419,11 +1471,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>56.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1433,7 +1485,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46033</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1445,11 +1497,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>57.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1459,7 +1511,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1471,11 +1523,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>56.39</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1485,11 +1537,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1501,21 +1553,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>54.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46180</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1523,11 +1575,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>53.01</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,11 +1589,11 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46055</v>
+        <v>46187</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1553,139 +1605,9 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>41.5</v>
+        <v>52.53</v>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1702,7 +1624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,7 +1677,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.26000000000001</v>
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1781,7 +1703,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.84</v>
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1791,7 +1713,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1803,11 +1725,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60.52</v>
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1817,7 +1739,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45955</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1829,11 +1751,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.15</v>
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1843,7 +1765,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46033</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1855,11 +1777,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.26</v>
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1869,7 +1791,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1881,11 +1803,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56.39</v>
+        <v>49.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1895,11 +1817,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>46130</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1911,21 +1833,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.31</v>
+        <v>50.03</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46180</v>
+        <v>46055</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1933,11 +1855,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53.01</v>
+        <v>48.34</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1947,25 +1869,129 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
         <v>46187</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>52.53</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バック" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -934,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>66.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1035,11 +1035,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>60.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45955</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1061,11 +1061,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>56.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46033</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1087,11 +1087,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>57.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>56.39</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,11 +1127,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>54.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46180</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>53.01</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46055</v>
+        <v>46187</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1195,139 +1195,9 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>41.5</v>
+        <v>52.53</v>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小4</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1344,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,7 +1267,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.26000000000001</v>
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1423,7 +1293,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.84</v>
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1433,7 +1303,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1445,11 +1315,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60.52</v>
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1459,7 +1329,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45955</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1471,11 +1341,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.15</v>
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1485,7 +1355,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46033</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1497,11 +1367,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.26</v>
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1511,7 +1381,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1523,11 +1393,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56.39</v>
+        <v>49.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,11 +1407,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>46130</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1553,21 +1423,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.31</v>
+        <v>50.03</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46180</v>
+        <v>46055</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1575,11 +1445,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53.01</v>
+        <v>48.34</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1589,25 +1459,129 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
         <v>46187</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>52.53</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1624,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1677,7 +1651,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.72</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1687,7 +1661,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1703,7 +1677,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56.3</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1729,7 +1703,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55.74</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1755,7 +1729,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.07</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1781,7 +1755,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52.11</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1791,7 +1765,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1807,7 +1781,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1833,7 +1807,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50.03</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1843,7 +1817,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46055</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1859,7 +1833,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48.34</v>
+        <v>42.36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1869,7 +1843,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46075</v>
+        <v>46055</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1881,11 +1855,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1895,11 +1869,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1907,21 +1881,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48.72</v>
+        <v>42.24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1937,17 +1911,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45.85</v>
+        <v>40.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>46179</v>
+        <v>46152</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1959,11 +1933,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.75</v>
+        <v>39.25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,25 +1947,77 @@
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
         <v>46187</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1598,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,6 +2023,32 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1598,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,32 +2023,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>50</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>40.06</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="バック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="フリー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="バック" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -934,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.26000000000001</v>
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.84</v>
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45844</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1035,11 +1035,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60.52</v>
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45955</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1061,11 +1061,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.15</v>
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46033</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1087,11 +1087,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.26</v>
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56.39</v>
+        <v>49.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,11 +1127,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>46130</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.31</v>
+        <v>50.03</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46180</v>
+        <v>46055</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53.01</v>
+        <v>48.34</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1179,25 +1179,129 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
         <v>46187</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>52.53</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1214,7 +1318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,7 +1371,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.72</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1277,7 +1381,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1293,7 +1397,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56.3</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1319,7 +1423,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55.74</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1345,7 +1449,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.07</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1371,7 +1475,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52.11</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1381,7 +1485,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1397,7 +1501,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1423,7 +1527,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50.03</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1537,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46055</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1449,7 +1553,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48.34</v>
+        <v>42.36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1459,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46075</v>
+        <v>46055</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1471,11 +1575,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1485,11 +1589,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1497,21 +1601,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48.72</v>
+        <v>42.24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1527,17 +1631,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45.85</v>
+        <v>40.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>46179</v>
+        <v>46152</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1549,11 +1653,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.75</v>
+        <v>39.25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,25 +1667,77 @@
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
         <v>46187</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1598,7 +1754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,7 +1807,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1661,7 +1817,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1677,7 +1833,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>66.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1687,7 +1843,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1699,11 +1855,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>60.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1713,7 +1869,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45955</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1725,11 +1881,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>56.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1739,7 +1895,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46033</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1751,11 +1907,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>57.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1765,7 +1921,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1777,11 +1933,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>56.39</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1791,11 +1947,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1807,21 +1963,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>54.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46180</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1829,11 +1985,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>53.01</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1843,11 +1999,11 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46055</v>
+        <v>46187</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1859,7 +2015,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>41.5</v>
+        <v>52.53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1869,11 +2025,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46075</v>
+        <v>46207</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1885,139 +2041,9 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>42.24</v>
+        <v>53.65</v>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>40.06</v>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -6,11 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="バッタ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="メドレー" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="バック" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="フリー" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ブレ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="メドレー" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,33 +505,35 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45823</v>
+        <v>45710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.49</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4'52"00</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45956</v>
+        <v>45808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -539,25 +541,27 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>52.07</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4'17"24</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45984</v>
+        <v>45899</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -565,25 +569,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>51.12</v>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3'50"98</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>46033</v>
+        <v>45991</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -591,25 +597,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>53</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3'44"22</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46055</v>
+        <v>46081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -617,95 +625,45 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>49.85</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3'35"70</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>46172</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53.89</v>
+        <v>207.18</v>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>52.64</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
         </is>
@@ -722,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,35 +717,33 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45710</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>小3</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4'52"00</t>
-        </is>
+      <c r="E2" t="n">
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45808</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -795,27 +751,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4'17"24</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45899</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -823,27 +777,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>短水路</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3'50"98</t>
-        </is>
+      <c r="E4" t="n">
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45991</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -851,27 +803,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3'44"22</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46081</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -879,47 +829,227 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3'35"70</t>
-        </is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46172</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>45984</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>207.18</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
@@ -934,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,7 +1117,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.72</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -997,7 +1127,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1013,7 +1143,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56.3</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1039,7 +1169,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55.74</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1065,7 +1195,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.07</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1221,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52.11</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1101,7 +1231,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1117,7 +1247,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1143,7 +1273,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50.03</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1153,7 +1283,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46055</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1169,7 +1299,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48.34</v>
+        <v>42.36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1179,7 +1309,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46075</v>
+        <v>46055</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1191,11 +1321,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1205,11 +1335,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1217,21 +1347,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48.72</v>
+        <v>42.24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1247,17 +1377,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45.85</v>
+        <v>40.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>46179</v>
+        <v>46152</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1269,11 +1399,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.75</v>
+        <v>39.25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1283,25 +1413,77 @@
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
         <v>46187</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1318,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,7 +1553,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1381,7 +1563,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1397,7 +1579,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>66.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1407,7 +1589,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1419,11 +1601,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>60.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1433,7 +1615,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45955</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1445,11 +1627,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>56.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1459,7 +1641,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46033</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1471,11 +1653,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>57.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1485,7 +1667,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1497,11 +1679,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>56.39</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1511,11 +1693,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1527,21 +1709,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>54.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46180</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1549,11 +1731,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>53.01</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1563,11 +1745,11 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46055</v>
+        <v>46187</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1579,7 +1761,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>41.5</v>
+        <v>52.53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1589,11 +1771,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46075</v>
+        <v>46207</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1605,139 +1787,9 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>42.24</v>
+        <v>53.65</v>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>40.06</v>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1754,7 +1806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,7 +1843,7 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1807,7 +1859,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.26000000000001</v>
+        <v>58.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1817,7 +1869,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1829,11 +1881,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.84</v>
+        <v>52.07</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1843,7 +1895,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45844</v>
+        <v>45984</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1859,7 +1911,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60.52</v>
+        <v>51.12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1869,7 +1921,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45955</v>
+        <v>46033</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1885,7 +1937,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.15</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1895,7 +1947,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46033</v>
+        <v>46055</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1911,7 +1963,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.26</v>
+        <v>49.85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1937,7 +1989,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56.39</v>
+        <v>53.89</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1959,11 +2011,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.31</v>
+        <v>52.64</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1973,7 +2025,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46180</v>
+        <v>46152</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1985,21 +2037,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53.01</v>
+        <v>49.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46187</v>
+        <v>46208</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2011,39 +2063,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>52.53</v>
+        <v>49.43</v>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="メドレー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="バック" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="フリー" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ブレ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="バッタ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="フリー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ブレ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="バッタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="バック" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -680,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.72</v>
+        <v>50.61</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>56.3</v>
+        <v>49.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55.74</v>
+        <v>48.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.07</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52.11</v>
+        <v>44.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45956</v>
+        <v>45955</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.12</v>
+        <v>43.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50.03</v>
+        <v>42.75</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46055</v>
+        <v>46033</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48.34</v>
+        <v>42.36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46075</v>
+        <v>46055</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -937,11 +937,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -951,11 +951,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46130</v>
+        <v>46075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -963,21 +963,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48.72</v>
+        <v>42.24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
-        <v>46152</v>
+        <v>46130</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -993,17 +993,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45.85</v>
+        <v>40.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
-        <v>46179</v>
+        <v>46152</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1015,11 +1015,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.75</v>
+        <v>39.25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1029,25 +1029,77 @@
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
         <v>46187</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1064,7 +1116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,7 +1169,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1127,7 +1179,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1143,7 +1195,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.82</v>
+        <v>66.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1153,7 +1205,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1165,11 +1217,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48.98</v>
+        <v>60.52</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1179,7 +1231,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45844</v>
+        <v>45955</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1191,11 +1243,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>56.15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1205,7 +1257,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>45942</v>
+        <v>46033</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1217,11 +1269,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44.07</v>
+        <v>57.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1231,7 +1283,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>45955</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1243,11 +1295,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43.01</v>
+        <v>56.39</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1257,11 +1309,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>45984</v>
+        <v>46130</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1273,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42.75</v>
+        <v>54.31</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46033</v>
+        <v>46180</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1295,11 +1347,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42.36</v>
+        <v>53.01</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1309,11 +1361,11 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46055</v>
+        <v>46187</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1325,7 +1377,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>41.5</v>
+        <v>52.53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1335,11 +1387,11 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
-        <v>46075</v>
+        <v>46207</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>小4</t>
+          <t>小5</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1351,139 +1403,9 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>42.24</v>
+        <v>53.65</v>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>46130</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>菰野スイミング</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="n">
-        <v>46180</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>短水路</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>40.06</v>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1500,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,7 +1459,7 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45788</v>
+        <v>45823</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1553,7 +1475,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>68.26000000000001</v>
+        <v>58.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1563,7 +1485,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45815</v>
+        <v>45956</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1575,11 +1497,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.84</v>
+        <v>52.07</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1589,7 +1511,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45844</v>
+        <v>45984</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1605,7 +1527,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60.52</v>
+        <v>51.12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1615,7 +1537,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>45955</v>
+        <v>46033</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1631,7 +1553,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.15</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1641,7 +1563,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46033</v>
+        <v>46055</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1657,7 +1579,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57.26</v>
+        <v>49.85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1683,7 +1605,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56.39</v>
+        <v>53.89</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1705,11 +1627,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54.31</v>
+        <v>52.64</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1719,7 +1641,7 @@
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46180</v>
+        <v>46152</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1731,21 +1653,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53.01</v>
+        <v>49.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>鈴鹿</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
-        <v>46187</v>
+        <v>46208</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1757,39 +1679,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>52.53</v>
+        <v>49.43</v>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>46207</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>50</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>
@@ -1806,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1843,7 +1739,7 @@
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
-        <v>45823</v>
+        <v>45788</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1859,7 +1755,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.49</v>
+        <v>58.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1869,7 +1765,7 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
-        <v>45956</v>
+        <v>45815</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1881,11 +1777,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52.07</v>
+        <v>56.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1895,7 +1791,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
-        <v>45984</v>
+        <v>45823</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1907,11 +1803,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>51.12</v>
+        <v>55.74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1921,7 +1817,7 @@
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
-        <v>46033</v>
+        <v>45844</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1933,11 +1829,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>56.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1947,7 +1843,7 @@
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
-        <v>46055</v>
+        <v>45942</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1959,11 +1855,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.85</v>
+        <v>52.11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1973,7 +1869,7 @@
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
-        <v>46075</v>
+        <v>45956</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1985,11 +1881,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>長水路</t>
+          <t>短水路</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53.89</v>
+        <v>49.12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1999,11 +1895,11 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
-        <v>46130</v>
+        <v>45984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2011,25 +1907,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>短水路</t>
+          <t>長水路</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>52.64</v>
+        <v>50.03</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
-        <v>46152</v>
+        <v>46055</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>小5</t>
+          <t>小4</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2041,35 +1937,165 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49.1</v>
+        <v>48.34</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>菰野スイミング</t>
+          <t>鈴鹿</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>小4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>菰野スイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>短水路</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
         <v>46208</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>小5</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>49.43</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="C15" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>鈴鹿</t>
         </is>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1702,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2101,6 +2101,32 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>小5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>長水路</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>鈴鹿</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/楓果記録.xlsx
+++ b/楓果記録.xlsx
@@ -1702,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2101,32 +2101,6 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>46208</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>小5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>50</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>長水路</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>47.77</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>鈴鹿</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
